--- a/АЧХ.xlsx
+++ b/АЧХ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732E8595-2C0E-4952-A7EF-7B3FEF4B729C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2CF1B8F-1449-4A51-8AEE-0F0980E0F227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2640" yWindow="195" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,30 +34,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
-  <si>
-    <t>Установленное значение при коэффициенте усиления 10</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>частота\канал</t>
-  </si>
-  <si>
-    <t>Измеренное значение при коэффициенте усиления 10</t>
-  </si>
-  <si>
-    <t>Погрешность при коеффициенте усления 10</t>
-  </si>
-  <si>
-    <t>Установленное значение при коэффициенте усиления 1</t>
   </si>
   <si>
     <t>частота/канал</t>
   </si>
   <si>
-    <t>Измеренное значение при коэффициенте усиления 1</t>
+    <t>Установленное значение при коэффициенте усиления BOE "-1", BOC "0"</t>
   </si>
   <si>
-    <t>Погрешность при коеффициенте усления 1</t>
+    <t>Измеренное значение при коэффициенте усиления BOE "-1", BOC "0"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "-1", BOC "0"</t>
+  </si>
+  <si>
+    <t>Установленное значение при коэффициенте усиления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Измеренное значение при коэффициенте усиления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "-1", BOC "3"</t>
+  </si>
+  <si>
+    <t>Установленное значение при коэффициенте усиления BOE "0", BOC "0"</t>
+  </si>
+  <si>
+    <t>Измеренное значение при коэффициенте усиления BOE "0", BOC "0"</t>
+  </si>
+  <si>
+    <t>Погрешность при коеффициенте усления BOE "0", BOC "0"</t>
   </si>
 </sst>
 </file>
@@ -68,13 +77,20 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -93,11 +109,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -105,251 +136,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -746,12 +538,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="20" width="13.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -761,10 +556,18 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -790,8 +593,16 @@
       <c r="I2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>50</v>
       </c>
@@ -827,8 +638,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>60</v>
       </c>
@@ -864,8 +683,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>70</v>
       </c>
@@ -901,8 +728,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>100</v>
       </c>
@@ -938,8 +773,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>140</v>
       </c>
@@ -975,8 +818,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>180</v>
       </c>
@@ -1012,8 +863,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>210</v>
       </c>
@@ -1049,8 +908,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>250</v>
       </c>
@@ -1086,10 +953,28 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1099,10 +984,18 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1128,8 +1021,16 @@
       <c r="I13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>50</v>
       </c>
@@ -1165,8 +1066,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>60</v>
       </c>
@@ -1202,8 +1111,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>70</v>
       </c>
@@ -1239,8 +1156,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>100</v>
       </c>
@@ -1276,8 +1201,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>140</v>
       </c>
@@ -1313,8 +1246,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>180</v>
       </c>
@@ -1350,8 +1291,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>210</v>
       </c>
@@ -1387,8 +1336,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>250</v>
       </c>
@@ -1424,10 +1381,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1437,10 +1412,18 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1466,17 +1449,25 @@
       <c r="I24">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>50</v>
       </c>
       <c r="B25" s="2" t="e">
-        <f>20*LOG(((B14/5)*B$6)/(B3*(B$17/5)), 10)</f>
+        <f>20*LOG(((B14)*B$6)/(B3*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C25" s="2" t="e">
-        <f t="shared" ref="C25:I25" si="4">20*LOG(((C14/5)*C$6)/(C3*(C$17/5)), 10)</f>
+        <f t="shared" ref="C25:I25" si="4">20*LOG(((C14)*C$6)/(C3*(C$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D25" s="2" t="e">
@@ -1503,13 +1494,21 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>60</v>
       </c>
       <c r="B26" s="2" t="e">
-        <f t="shared" ref="B26:I32" si="5">20*LOG(((B15/5)*B$6)/(B4*(B$17/5)), 10)</f>
+        <f t="shared" ref="B26:I26" si="5">20*LOG(((B15)*B$6)/(B4*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C26" s="2" t="e">
@@ -1540,232 +1539,308 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>70</v>
       </c>
       <c r="B27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B27:I27" si="6">20*LOG(((B16)*B$6)/(B5*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>100</v>
       </c>
       <c r="B28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B28:I28" si="7">20*LOG(((B17)*B$6)/(B6*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>140</v>
       </c>
       <c r="B29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B29:I29" si="8">20*LOG(((B18)*B$6)/(B7*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H29" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I29" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>180</v>
       </c>
       <c r="B30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B30:I30" si="9">20*LOG(((B19)*B$6)/(B8*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I30" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>210</v>
       </c>
       <c r="B31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B31:I31" si="10">20*LOG(((B20)*B$6)/(B9*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>250</v>
       </c>
       <c r="B32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B32:I32" si="11">20*LOG(((B21)*B$6)/(B10*(B$17)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="2" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="2" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1775,10 +1850,18 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1804,304 +1887,386 @@
       <c r="I36">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>50</v>
       </c>
       <c r="B37" s="1">
-        <f t="shared" ref="B37:I44" si="6">M17</f>
+        <f t="shared" ref="B37:I44" si="12">M17</f>
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>60</v>
       </c>
       <c r="B38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>70</v>
       </c>
       <c r="B39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>100</v>
       </c>
       <c r="B40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>140</v>
       </c>
       <c r="B41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>180</v>
       </c>
       <c r="B42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>210</v>
       </c>
       <c r="B43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>250</v>
       </c>
       <c r="B44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
@@ -2113,10 +2278,18 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2142,78 +2315,94 @@
       <c r="I47">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>50</v>
       </c>
       <c r="B48" s="1">
-        <f t="shared" ref="B48:I55" si="7">M25</f>
+        <f t="shared" ref="B48:I55" si="13">M25</f>
         <v>0</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>60</v>
       </c>
       <c r="B49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2222,35 +2411,35 @@
         <v>70</v>
       </c>
       <c r="B50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2259,35 +2448,35 @@
         <v>100</v>
       </c>
       <c r="B51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2296,35 +2485,35 @@
         <v>140</v>
       </c>
       <c r="B52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2333,35 +2522,35 @@
         <v>180</v>
       </c>
       <c r="B53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2370,35 +2559,35 @@
         <v>210</v>
       </c>
       <c r="B54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2407,35 +2596,35 @@
         <v>250</v>
       </c>
       <c r="B55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="C55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2454,7 +2643,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2486,35 +2675,35 @@
         <v>50</v>
       </c>
       <c r="B59" s="2" t="e">
-        <f>20*LOG(((B48/5)*B$40)/(B37*(B$51/5)), 10)</f>
+        <f>20*LOG(((B48)*B$40)/(B37*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C59" s="2" t="e">
-        <f t="shared" ref="C59:I59" si="8">20*LOG(((C48/5)*C$40)/(C37*(C$51/5)), 10)</f>
+        <f t="shared" ref="C59:I59" si="14">20*LOG(((C48)*C$40)/(C37*(C$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I59" s="2" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2523,35 +2712,35 @@
         <v>60</v>
       </c>
       <c r="B60" s="2" t="e">
-        <f>20*LOG(((B49/5)*B$40)/(B38*(B$51/5)), 10)</f>
+        <f t="shared" ref="B60:I60" si="15">20*LOG(((B49)*B$40)/(B38*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C60" s="2" t="e">
-        <f t="shared" ref="B60:I66" si="9">20*LOG(((C49/5)*C$40)/(C38*(C$51/5)), 10)</f>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I60" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2560,35 +2749,35 @@
         <v>70</v>
       </c>
       <c r="B61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B61:I61" si="16">20*LOG(((B50)*B$40)/(B39*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I61" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2597,35 +2786,35 @@
         <v>100</v>
       </c>
       <c r="B62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B62:I62" si="17">20*LOG(((B51)*B$40)/(B40*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I62" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2634,35 +2823,35 @@
         <v>140</v>
       </c>
       <c r="B63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B63:I63" si="18">20*LOG(((B52)*B$40)/(B41*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I63" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2671,35 +2860,35 @@
         <v>180</v>
       </c>
       <c r="B64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B64:I64" si="19">20*LOG(((B53)*B$40)/(B42*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I64" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2708,35 +2897,35 @@
         <v>210</v>
       </c>
       <c r="B65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B65:I65" si="20">20*LOG(((B54)*B$40)/(B43*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I65" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2745,40 +2934,1057 @@
         <v>250</v>
       </c>
       <c r="B66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="B66:I66" si="21">20*LOG(((B55)*B$40)/(B44*(B$51)), 10)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I66" s="2" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <v>7</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>50</v>
+      </c>
+      <c r="B70" s="1">
+        <f>M33</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" ref="C70:I70" si="22">N33</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>60</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" ref="B71:B77" si="23">M34</f>
+        <v>0</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" ref="C71:C77" si="24">N34</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" ref="D71:D77" si="25">O34</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" ref="E71:E77" si="26">P34</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" ref="F71:F77" si="27">Q34</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <f t="shared" ref="G71:G77" si="28">R34</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <f t="shared" ref="H71:H77" si="29">S34</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" ref="I71:I77" si="30">T34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>100</v>
+      </c>
+      <c r="B73" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>140</v>
+      </c>
+      <c r="B74" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>180</v>
+      </c>
+      <c r="B75" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C75" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>210</v>
+      </c>
+      <c r="B76" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>250</v>
+      </c>
+      <c r="B77" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>7</v>
+      </c>
+      <c r="I80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>50</v>
+      </c>
+      <c r="B81" s="1">
+        <f>M41</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="1">
+        <f t="shared" ref="C81:I81" si="31">N41</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>60</v>
+      </c>
+      <c r="B82" s="1">
+        <f t="shared" ref="B82:B88" si="32">M42</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="1">
+        <f t="shared" ref="C82:C88" si="33">N42</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" ref="D82:D88" si="34">O42</f>
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <f t="shared" ref="E82:E88" si="35">P42</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" ref="F82:F88" si="36">Q42</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" ref="G82:G88" si="37">R42</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <f t="shared" ref="H82:H88" si="38">S42</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <f t="shared" ref="I82:I88" si="39">T42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>70</v>
+      </c>
+      <c r="B83" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>100</v>
+      </c>
+      <c r="B84" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>140</v>
+      </c>
+      <c r="B85" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>180</v>
+      </c>
+      <c r="B86" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>210</v>
+      </c>
+      <c r="B87" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E87" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H87" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>250</v>
+      </c>
+      <c r="B88" s="1">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="1">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91">
+        <v>5</v>
+      </c>
+      <c r="G91">
+        <v>6</v>
+      </c>
+      <c r="H91">
+        <v>7</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>50</v>
+      </c>
+      <c r="B92" s="2" t="e">
+        <f>20*LOG(((B81/5)*B$73)/(B70*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C92" s="2" t="e">
+        <f t="shared" ref="C92:I92" si="40">20*LOG(((C81/5)*C$73)/(C70*(C$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I92" s="2" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>60</v>
+      </c>
+      <c r="B93" s="2" t="e">
+        <f t="shared" ref="B93:I93" si="41">20*LOG(((B82/5)*B$73)/(B71*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I93" s="2" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>70</v>
+      </c>
+      <c r="B94" s="2" t="e">
+        <f t="shared" ref="B94:I94" si="42">20*LOG(((B83/5)*B$73)/(B72*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I94" s="2" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>100</v>
+      </c>
+      <c r="B95" s="2" t="e">
+        <f t="shared" ref="B95:I95" si="43">20*LOG(((B84/5)*B$73)/(B73*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I95" s="2" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>140</v>
+      </c>
+      <c r="B96" s="2" t="e">
+        <f t="shared" ref="B96:I96" si="44">20*LOG(((B85/5)*B$73)/(B74*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I96" s="2" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>180</v>
+      </c>
+      <c r="B97" s="2" t="e">
+        <f t="shared" ref="B97:I97" si="45">20*LOG(((B86/5)*B$73)/(B75*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I97" s="2" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>210</v>
+      </c>
+      <c r="B98" s="2" t="e">
+        <f t="shared" ref="B98:I98" si="46">20*LOG(((B87/5)*B$73)/(B76*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I98" s="2" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>250</v>
+      </c>
+      <c r="B99" s="2" t="e">
+        <f t="shared" ref="B99:I99" si="47">20*LOG(((B88/5)*B$73)/(B77*(B$84/5)), 10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H99" s="2" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I99" s="2" t="e">
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A90:I90"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A12:I12"/>
@@ -2786,42 +3992,62 @@
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A46:I46"/>
   </mergeCells>
-  <conditionalFormatting sqref="B59:I66">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="greaterThan">
+  <conditionalFormatting sqref="B25:I32">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="lessThan">
+      <formula>-5.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:I32">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59:I59 B66:I66">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="B26:I26 B31:I31">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
+      <formula>-2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:I30">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:I66">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
       <formula>-5.5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B59:I66">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B60:I60 B65:I65">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="lessThan">
       <formula>-2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:I64">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:I32">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="B92:I99">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>-5.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92:I99">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:I25 B32:I32">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
-      <formula>-5.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:I26 B31:I31">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="B93:I93 B98:I98">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>-2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27:I30">
+  <conditionalFormatting sqref="B94:I97">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>-0.5</formula>
     </cfRule>
